--- a/examples/output/demo_fragrance_reviews_report.xlsx
+++ b/examples/output/demo_fragrance_reviews_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5787" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5799" uniqueCount="144">
   <si>
     <t>Field</t>
   </si>
@@ -75,10 +75,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.2</t>
   </si>
   <si>
-    <t>2026-09-17T09:35:39</t>
+    <t>2026-09-17T11:50:16</t>
   </si>
   <si>
     <t>Identifying columns (names, emails, locations, IPs, order ids) were removed at ingest. Spend is shown only as a band. Emails, phones, URLs and handles inside answers are masked.</t>
@@ -276,6 +276,15 @@
     <t>no_concern</t>
   </si>
   <si>
+    <t>first_time_trial</t>
+  </si>
+  <si>
+    <t>loyalty_rewards</t>
+  </si>
+  <si>
+    <t>site_usability</t>
+  </si>
+  <si>
     <t>Efficacy &amp; results</t>
   </si>
   <si>
@@ -307,6 +316,15 @@
   </si>
   <si>
     <t>Nothing / no concern</t>
+  </si>
+  <si>
+    <t>First-time trial</t>
+  </si>
+  <si>
+    <t>Loyalty &amp; rewards</t>
+  </si>
+  <si>
+    <t>Site &amp; buying experience</t>
   </si>
   <si>
     <t>Precio y valor</t>
@@ -363,6 +381,15 @@
     <t>Ninguna / sin inquietud</t>
   </si>
   <si>
+    <t>Primera compra / probar la marca</t>
+  </si>
+  <si>
+    <t>Lealtad y recompensas</t>
+  </si>
+  <si>
+    <t>Experiencia de compra en el sitio</t>
+  </si>
+  <si>
     <t>Price, discounts, promotions, or value for money.</t>
   </si>
   <si>
@@ -415,6 +442,15 @@
   </si>
   <si>
     <t>The customer explicitly had no concern or nothing to add.</t>
+  </si>
+  <si>
+    <t>Curiosity or trying the brand for the first time, with no prior experience of it.</t>
+  </si>
+  <si>
+    <t>Loyalty points, rewards, referral credit, memberships, subscriptions.</t>
+  </si>
+  <si>
+    <t>How easy the store itself is to use: finding things, the size selector, the cart, errors, unclear labels or steps.</t>
   </si>
 </sst>
 </file>
@@ -22205,13 +22241,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="27.7109375" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="71.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" customWidth="1"/>
+    <col min="4" max="4" width="80.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22236,10 +22272,10 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -22250,10 +22286,10 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -22261,13 +22297,13 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -22275,13 +22311,13 @@
         <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -22289,13 +22325,13 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -22306,10 +22342,10 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -22317,13 +22353,13 @@
         <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -22331,13 +22367,13 @@
         <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -22345,13 +22381,13 @@
         <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -22362,10 +22398,10 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -22376,10 +22412,10 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -22387,13 +22423,13 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -22401,13 +22437,13 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -22418,10 +22454,10 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -22432,10 +22468,10 @@
         <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -22443,13 +22479,13 @@
         <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -22457,13 +22493,13 @@
         <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -22471,13 +22507,55 @@
         <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
